--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>126054738</v>
       </c>
       <c r="B4" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1351,32 +1351,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126370532</v>
+        <v>126371162</v>
       </c>
       <c r="B8" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1386,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535396</v>
+        <v>535354</v>
       </c>
       <c r="R8" t="n">
-        <v>6722329</v>
+        <v>6722340</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,32 +1458,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126371162</v>
+        <v>126370532</v>
       </c>
       <c r="B9" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535354</v>
+        <v>535396</v>
       </c>
       <c r="R9" t="n">
-        <v>6722340</v>
+        <v>6722329</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1896,64 +1896,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126053951</v>
+        <v>126051559</v>
       </c>
       <c r="B13" t="n">
-        <v>98361</v>
+        <v>8447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535458</v>
+        <v>535369</v>
       </c>
       <c r="R13" t="n">
-        <v>6722324</v>
+        <v>6722495</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1982,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,7 +1985,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2013,55 +1996,71 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126051559</v>
+        <v>126053951</v>
       </c>
       <c r="B14" t="n">
-        <v>8447</v>
+        <v>98436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>535369</v>
+        <v>535458</v>
       </c>
       <c r="R14" t="n">
-        <v>6722495</v>
+        <v>6722324</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2090,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2100,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,6 +2108,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>126054738</v>
       </c>
       <c r="B4" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1351,32 +1351,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126371162</v>
+        <v>126370532</v>
       </c>
       <c r="B8" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1386,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535354</v>
+        <v>535396</v>
       </c>
       <c r="R8" t="n">
-        <v>6722340</v>
+        <v>6722329</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,32 +1458,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126370532</v>
+        <v>126371162</v>
       </c>
       <c r="B9" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535396</v>
+        <v>535354</v>
       </c>
       <c r="R9" t="n">
-        <v>6722329</v>
+        <v>6722340</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2006,7 +2006,7 @@
         <v>126053951</v>
       </c>
       <c r="B14" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126370384</v>
+        <v>126054200</v>
       </c>
       <c r="B2" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Högtäkt, Högtäkt, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535401</v>
+        <v>535583</v>
       </c>
       <c r="R2" t="n">
-        <v>6722359</v>
+        <v>6722243</v>
       </c>
       <c r="S2" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,55 +775,55 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126054200</v>
+        <v>126370384</v>
       </c>
       <c r="B3" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högtäkt, Högtäkt, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535583</v>
+        <v>535401</v>
       </c>
       <c r="R3" t="n">
-        <v>6722243</v>
+        <v>6722359</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>126054738</v>
       </c>
       <c r="B4" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1244,32 +1244,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126370901</v>
+        <v>126371162</v>
       </c>
       <c r="B7" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535355</v>
+        <v>535354</v>
       </c>
       <c r="R7" t="n">
-        <v>6722318</v>
+        <v>6722340</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,7 +1351,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126370532</v>
+        <v>126370901</v>
       </c>
       <c r="B8" t="n">
         <v>57654</v>
@@ -1386,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535396</v>
+        <v>535355</v>
       </c>
       <c r="R8" t="n">
-        <v>6722329</v>
+        <v>6722318</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,32 +1458,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126371162</v>
+        <v>126370532</v>
       </c>
       <c r="B9" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535354</v>
+        <v>535396</v>
       </c>
       <c r="R9" t="n">
-        <v>6722340</v>
+        <v>6722329</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2006,7 +2006,7 @@
         <v>126053951</v>
       </c>
       <c r="B14" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126054200</v>
+        <v>126370384</v>
       </c>
       <c r="B2" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Högtäkt, Högtäkt, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535583</v>
+        <v>535401</v>
       </c>
       <c r="R2" t="n">
-        <v>6722243</v>
+        <v>6722359</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,55 +775,55 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126370384</v>
+        <v>126054200</v>
       </c>
       <c r="B3" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Högtäkt, Högtäkt, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535401</v>
+        <v>535583</v>
       </c>
       <c r="R3" t="n">
-        <v>6722359</v>
+        <v>6722243</v>
       </c>
       <c r="S3" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1896,48 +1896,64 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126051559</v>
+        <v>126053951</v>
       </c>
       <c r="B13" t="n">
-        <v>8447</v>
+        <v>98443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535369</v>
+        <v>535458</v>
       </c>
       <c r="R13" t="n">
-        <v>6722495</v>
+        <v>6722324</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,6 +2001,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1996,71 +2013,55 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126053951</v>
+        <v>126051559</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>8447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>535458</v>
+        <v>535369</v>
       </c>
       <c r="R14" t="n">
-        <v>6722324</v>
+        <v>6722495</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2089,7 +2090,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2100,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2108,7 +2109,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126370384</v>
+        <v>126054200</v>
       </c>
       <c r="B2" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Högtäkt, Högtäkt, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535401</v>
+        <v>535583</v>
       </c>
       <c r="R2" t="n">
-        <v>6722359</v>
+        <v>6722243</v>
       </c>
       <c r="S2" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,55 +775,55 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126054200</v>
+        <v>126370384</v>
       </c>
       <c r="B3" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högtäkt, Högtäkt, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535583</v>
+        <v>535401</v>
       </c>
       <c r="R3" t="n">
-        <v>6722243</v>
+        <v>6722359</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1015,38 +1015,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126051392</v>
+        <v>126050897</v>
       </c>
       <c r="B5" t="n">
-        <v>57654</v>
+        <v>56849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535382</v>
+        <v>535233</v>
       </c>
       <c r="R5" t="n">
-        <v>6722489</v>
+        <v>6722467</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På hranstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,45 +1125,45 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126050897</v>
+        <v>126051392</v>
       </c>
       <c r="B6" t="n">
-        <v>56849</v>
+        <v>57654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1167,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535233</v>
+        <v>535382</v>
       </c>
       <c r="R6" t="n">
-        <v>6722467</v>
+        <v>6722489</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,12 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På hranstubbe</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1896,64 +1896,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126053951</v>
+        <v>126051559</v>
       </c>
       <c r="B13" t="n">
-        <v>98443</v>
+        <v>8447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535458</v>
+        <v>535369</v>
       </c>
       <c r="R13" t="n">
-        <v>6722324</v>
+        <v>6722495</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1982,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,7 +1985,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2013,55 +1996,71 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126051559</v>
+        <v>126053951</v>
       </c>
       <c r="B14" t="n">
-        <v>8447</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>535369</v>
+        <v>535458</v>
       </c>
       <c r="R14" t="n">
-        <v>6722495</v>
+        <v>6722324</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2090,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2100,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,6 +2108,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -1015,38 +1015,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126050897</v>
+        <v>126051392</v>
       </c>
       <c r="B5" t="n">
-        <v>56849</v>
+        <v>57654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535233</v>
+        <v>535382</v>
       </c>
       <c r="R5" t="n">
-        <v>6722467</v>
+        <v>6722489</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,12 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På hranstubbe</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,45 +1120,45 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126051392</v>
+        <v>126050897</v>
       </c>
       <c r="B6" t="n">
-        <v>57654</v>
+        <v>56849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1172,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535382</v>
+        <v>535233</v>
       </c>
       <c r="R6" t="n">
-        <v>6722489</v>
+        <v>6722467</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1212,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På hranstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,39 +1237,39 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126371162</v>
+        <v>126370901</v>
       </c>
       <c r="B7" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535354</v>
+        <v>535355</v>
       </c>
       <c r="R7" t="n">
-        <v>6722340</v>
+        <v>6722318</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,7 +1351,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126370901</v>
+        <v>126370532</v>
       </c>
       <c r="B8" t="n">
         <v>57654</v>
@@ -1386,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535355</v>
+        <v>535396</v>
       </c>
       <c r="R8" t="n">
-        <v>6722318</v>
+        <v>6722329</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,32 +1458,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126370532</v>
+        <v>126371162</v>
       </c>
       <c r="B9" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535396</v>
+        <v>535354</v>
       </c>
       <c r="R9" t="n">
-        <v>6722329</v>
+        <v>6722340</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -1244,32 +1244,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126370901</v>
+        <v>126371162</v>
       </c>
       <c r="B7" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535355</v>
+        <v>535354</v>
       </c>
       <c r="R7" t="n">
-        <v>6722318</v>
+        <v>6722340</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,7 +1351,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126370532</v>
+        <v>126370901</v>
       </c>
       <c r="B8" t="n">
         <v>57654</v>
@@ -1386,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535396</v>
+        <v>535355</v>
       </c>
       <c r="R8" t="n">
-        <v>6722329</v>
+        <v>6722318</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,32 +1458,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126371162</v>
+        <v>126370532</v>
       </c>
       <c r="B9" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535354</v>
+        <v>535396</v>
       </c>
       <c r="R9" t="n">
-        <v>6722340</v>
+        <v>6722329</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1896,48 +1896,64 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126051559</v>
+        <v>126053951</v>
       </c>
       <c r="B13" t="n">
-        <v>8447</v>
+        <v>98443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535369</v>
+        <v>535458</v>
       </c>
       <c r="R13" t="n">
-        <v>6722495</v>
+        <v>6722324</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,6 +2001,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1996,71 +2013,55 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126053951</v>
+        <v>126051559</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>8447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>535458</v>
+        <v>535369</v>
       </c>
       <c r="R14" t="n">
-        <v>6722324</v>
+        <v>6722495</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2089,7 +2090,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2100,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2108,7 +2109,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126054200</v>
+        <v>126370384</v>
       </c>
       <c r="B2" t="n">
-        <v>57654</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Högtäkt, Högtäkt, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535583</v>
+        <v>535401</v>
       </c>
       <c r="R2" t="n">
-        <v>6722243</v>
+        <v>6722359</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,55 +775,55 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126370384</v>
+        <v>126054200</v>
       </c>
       <c r="B3" t="n">
-        <v>8447</v>
+        <v>57658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Högtäkt, Högtäkt, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535401</v>
+        <v>535583</v>
       </c>
       <c r="R3" t="n">
-        <v>6722359</v>
+        <v>6722243</v>
       </c>
       <c r="S3" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -892,7 +892,7 @@
         <v>126054738</v>
       </c>
       <c r="B4" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>126051392</v>
       </c>
       <c r="B5" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>126050897</v>
       </c>
       <c r="B6" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,32 +1244,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126371162</v>
+        <v>126370901</v>
       </c>
       <c r="B7" t="n">
-        <v>8447</v>
+        <v>57658</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535354</v>
+        <v>535355</v>
       </c>
       <c r="R7" t="n">
-        <v>6722340</v>
+        <v>6722318</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126370901</v>
+        <v>126370532</v>
       </c>
       <c r="B8" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535355</v>
+        <v>535396</v>
       </c>
       <c r="R8" t="n">
-        <v>6722318</v>
+        <v>6722329</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,32 +1458,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126370532</v>
+        <v>126371162</v>
       </c>
       <c r="B9" t="n">
-        <v>57654</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535396</v>
+        <v>535354</v>
       </c>
       <c r="R9" t="n">
-        <v>6722329</v>
+        <v>6722340</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,7 +1568,7 @@
         <v>126053829</v>
       </c>
       <c r="B10" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>126051147</v>
       </c>
       <c r="B11" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>126053644</v>
       </c>
       <c r="B12" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,64 +1896,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126053951</v>
+        <v>126051559</v>
       </c>
       <c r="B13" t="n">
-        <v>98443</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535458</v>
+        <v>535369</v>
       </c>
       <c r="R13" t="n">
-        <v>6722324</v>
+        <v>6722495</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1982,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,7 +1985,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2013,55 +1996,71 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126051559</v>
+        <v>126053951</v>
       </c>
       <c r="B14" t="n">
-        <v>8447</v>
+        <v>98447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>535369</v>
+        <v>535458</v>
       </c>
       <c r="R14" t="n">
-        <v>6722495</v>
+        <v>6722324</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2090,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2100,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,6 +2108,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2130,7 +2130,7 @@
         <v>126372830</v>
       </c>
       <c r="B15" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126370384</v>
+        <v>126054200</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>57658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Högtäkt, Högtäkt, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535401</v>
+        <v>535583</v>
       </c>
       <c r="R2" t="n">
-        <v>6722359</v>
+        <v>6722243</v>
       </c>
       <c r="S2" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,55 +775,55 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126054200</v>
+        <v>126370384</v>
       </c>
       <c r="B3" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högtäkt, Högtäkt, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535583</v>
+        <v>535401</v>
       </c>
       <c r="R3" t="n">
-        <v>6722243</v>
+        <v>6722359</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1015,38 +1015,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126051392</v>
+        <v>126050897</v>
       </c>
       <c r="B5" t="n">
-        <v>57658</v>
+        <v>56853</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535382</v>
+        <v>535233</v>
       </c>
       <c r="R5" t="n">
-        <v>6722489</v>
+        <v>6722467</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På hranstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,45 +1125,45 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126050897</v>
+        <v>126051392</v>
       </c>
       <c r="B6" t="n">
-        <v>56853</v>
+        <v>57658</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1167,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535233</v>
+        <v>535382</v>
       </c>
       <c r="R6" t="n">
-        <v>6722467</v>
+        <v>6722489</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,12 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På hranstubbe</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -1015,38 +1015,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126050897</v>
+        <v>126051392</v>
       </c>
       <c r="B5" t="n">
-        <v>56853</v>
+        <v>57658</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535233</v>
+        <v>535382</v>
       </c>
       <c r="R5" t="n">
-        <v>6722467</v>
+        <v>6722489</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,12 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På hranstubbe</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,45 +1120,45 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126051392</v>
+        <v>126050897</v>
       </c>
       <c r="B6" t="n">
-        <v>57658</v>
+        <v>56853</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1172,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535382</v>
+        <v>535233</v>
       </c>
       <c r="R6" t="n">
-        <v>6722489</v>
+        <v>6722467</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1212,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På hranstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>126054738</v>
       </c>
       <c r="B4" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>126053951</v>
       </c>
       <c r="B14" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126054200</v>
+        <v>126370384</v>
       </c>
       <c r="B2" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Högtäkt, Högtäkt, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535583</v>
+        <v>535401</v>
       </c>
       <c r="R2" t="n">
-        <v>6722243</v>
+        <v>6722359</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,55 +775,55 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126370384</v>
+        <v>126054200</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>57658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Högtäkt, Högtäkt, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535401</v>
+        <v>535583</v>
       </c>
       <c r="R3" t="n">
-        <v>6722359</v>
+        <v>6722243</v>
       </c>
       <c r="S3" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1244,7 +1244,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126370901</v>
+        <v>126370532</v>
       </c>
       <c r="B7" t="n">
         <v>57658</v>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535355</v>
+        <v>535396</v>
       </c>
       <c r="R7" t="n">
-        <v>6722318</v>
+        <v>6722329</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,7 +1351,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126370532</v>
+        <v>126370901</v>
       </c>
       <c r="B8" t="n">
         <v>57658</v>
@@ -1386,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535396</v>
+        <v>535355</v>
       </c>
       <c r="R8" t="n">
-        <v>6722329</v>
+        <v>6722318</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126370384</v>
+        <v>126054200</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Högtäkt, Högtäkt, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535401</v>
+        <v>535583</v>
       </c>
       <c r="R2" t="n">
-        <v>6722359</v>
+        <v>6722243</v>
       </c>
       <c r="S2" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,55 +775,55 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126054200</v>
+        <v>126370384</v>
       </c>
       <c r="B3" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högtäkt, Högtäkt, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535583</v>
+        <v>535401</v>
       </c>
       <c r="R3" t="n">
-        <v>6722243</v>
+        <v>6722359</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -892,7 +892,7 @@
         <v>126054738</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,38 +1015,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126051392</v>
+        <v>126050897</v>
       </c>
       <c r="B5" t="n">
-        <v>57658</v>
+        <v>56855</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535382</v>
+        <v>535233</v>
       </c>
       <c r="R5" t="n">
-        <v>6722489</v>
+        <v>6722467</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På hranstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,45 +1125,45 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126050897</v>
+        <v>126051392</v>
       </c>
       <c r="B6" t="n">
-        <v>56853</v>
+        <v>57660</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1167,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535233</v>
+        <v>535382</v>
       </c>
       <c r="R6" t="n">
-        <v>6722467</v>
+        <v>6722489</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,12 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På hranstubbe</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,39 +1237,39 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126370532</v>
+        <v>126371162</v>
       </c>
       <c r="B7" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535396</v>
+        <v>535354</v>
       </c>
       <c r="R7" t="n">
-        <v>6722329</v>
+        <v>6722340</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,7 +1354,7 @@
         <v>126370901</v>
       </c>
       <c r="B8" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,32 +1458,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126371162</v>
+        <v>126370532</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535354</v>
+        <v>535396</v>
       </c>
       <c r="R9" t="n">
-        <v>6722340</v>
+        <v>6722329</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,7 +1568,7 @@
         <v>126053829</v>
       </c>
       <c r="B10" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>126051147</v>
       </c>
       <c r="B11" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>126053644</v>
       </c>
       <c r="B12" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>126053951</v>
       </c>
       <c r="B14" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126054200</v>
+        <v>126370384</v>
       </c>
       <c r="B2" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Högtäkt, Högtäkt, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535583</v>
+        <v>535401</v>
       </c>
       <c r="R2" t="n">
-        <v>6722243</v>
+        <v>6722359</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,55 +775,55 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126370384</v>
+        <v>126054200</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Högtäkt, Högtäkt, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535401</v>
+        <v>535583</v>
       </c>
       <c r="R3" t="n">
-        <v>6722359</v>
+        <v>6722243</v>
       </c>
       <c r="S3" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1015,38 +1015,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126050897</v>
+        <v>126051392</v>
       </c>
       <c r="B5" t="n">
-        <v>56855</v>
+        <v>57660</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535233</v>
+        <v>535382</v>
       </c>
       <c r="R5" t="n">
-        <v>6722467</v>
+        <v>6722489</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,12 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På hranstubbe</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,45 +1120,45 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126051392</v>
+        <v>126050897</v>
       </c>
       <c r="B6" t="n">
-        <v>57660</v>
+        <v>56855</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1172,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535382</v>
+        <v>535233</v>
       </c>
       <c r="R6" t="n">
-        <v>6722489</v>
+        <v>6722467</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1212,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På hranstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,39 +1237,39 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126371162</v>
+        <v>126370901</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535354</v>
+        <v>535355</v>
       </c>
       <c r="R7" t="n">
-        <v>6722340</v>
+        <v>6722318</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,7 +1351,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126370901</v>
+        <v>126370532</v>
       </c>
       <c r="B8" t="n">
         <v>57660</v>
@@ -1386,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535355</v>
+        <v>535396</v>
       </c>
       <c r="R8" t="n">
-        <v>6722318</v>
+        <v>6722329</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,32 +1458,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126370532</v>
+        <v>126371162</v>
       </c>
       <c r="B9" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535396</v>
+        <v>535354</v>
       </c>
       <c r="R9" t="n">
-        <v>6722329</v>
+        <v>6722340</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -1896,48 +1896,64 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126051559</v>
+        <v>126053951</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>98450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535369</v>
+        <v>535458</v>
       </c>
       <c r="R13" t="n">
-        <v>6722495</v>
+        <v>6722324</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,6 +2001,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1996,71 +2013,55 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126053951</v>
+        <v>126051559</v>
       </c>
       <c r="B14" t="n">
-        <v>98450</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>535458</v>
+        <v>535369</v>
       </c>
       <c r="R14" t="n">
-        <v>6722324</v>
+        <v>6722495</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2089,7 +2090,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2100,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2108,7 +2109,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -1896,64 +1896,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126053951</v>
+        <v>126051559</v>
       </c>
       <c r="B13" t="n">
-        <v>98450</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535458</v>
+        <v>535369</v>
       </c>
       <c r="R13" t="n">
-        <v>6722324</v>
+        <v>6722495</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1982,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,7 +1985,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2013,55 +1996,71 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126051559</v>
+        <v>126053951</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>98450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>535369</v>
+        <v>535458</v>
       </c>
       <c r="R14" t="n">
-        <v>6722495</v>
+        <v>6722324</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2090,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2100,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,6 +2108,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>126054738</v>
       </c>
       <c r="B4" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,38 +1015,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126051392</v>
+        <v>126050897</v>
       </c>
       <c r="B5" t="n">
-        <v>57660</v>
+        <v>56855</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535382</v>
+        <v>535233</v>
       </c>
       <c r="R5" t="n">
-        <v>6722489</v>
+        <v>6722467</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På hranstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,45 +1125,45 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126050897</v>
+        <v>126051392</v>
       </c>
       <c r="B6" t="n">
-        <v>56855</v>
+        <v>57660</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1167,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535233</v>
+        <v>535382</v>
       </c>
       <c r="R6" t="n">
-        <v>6722467</v>
+        <v>6722489</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,12 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På hranstubbe</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -2006,7 +2006,7 @@
         <v>126053951</v>
       </c>
       <c r="B14" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126370384</v>
+        <v>126054200</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Högtäkt, Högtäkt, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535401</v>
+        <v>535583</v>
       </c>
       <c r="R2" t="n">
-        <v>6722359</v>
+        <v>6722243</v>
       </c>
       <c r="S2" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,55 +775,55 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126054200</v>
+        <v>126370384</v>
       </c>
       <c r="B3" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högtäkt, Högtäkt, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535583</v>
+        <v>535401</v>
       </c>
       <c r="R3" t="n">
-        <v>6722243</v>
+        <v>6722359</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -892,7 +892,7 @@
         <v>126054738</v>
       </c>
       <c r="B4" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,38 +1015,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126050897</v>
+        <v>126051392</v>
       </c>
       <c r="B5" t="n">
-        <v>56855</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535233</v>
+        <v>535382</v>
       </c>
       <c r="R5" t="n">
-        <v>6722467</v>
+        <v>6722489</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,12 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På hranstubbe</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,45 +1120,45 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126051392</v>
+        <v>126050897</v>
       </c>
       <c r="B6" t="n">
-        <v>57660</v>
+        <v>56858</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1172,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535382</v>
+        <v>535233</v>
       </c>
       <c r="R6" t="n">
-        <v>6722489</v>
+        <v>6722467</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1212,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På hranstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1247,7 +1247,7 @@
         <v>126370901</v>
       </c>
       <c r="B7" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,32 +1351,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126370532</v>
+        <v>126371162</v>
       </c>
       <c r="B8" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1386,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535396</v>
+        <v>535354</v>
       </c>
       <c r="R8" t="n">
-        <v>6722329</v>
+        <v>6722340</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,32 +1458,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126371162</v>
+        <v>126370532</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535354</v>
+        <v>535396</v>
       </c>
       <c r="R9" t="n">
-        <v>6722340</v>
+        <v>6722329</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,7 +1568,7 @@
         <v>126053829</v>
       </c>
       <c r="B10" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>126051147</v>
       </c>
       <c r="B11" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>126053644</v>
       </c>
       <c r="B12" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,48 +1896,64 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126051559</v>
+        <v>126053951</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>98459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535369</v>
+        <v>535458</v>
       </c>
       <c r="R13" t="n">
-        <v>6722495</v>
+        <v>6722324</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,6 +2001,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1996,71 +2013,55 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126053951</v>
+        <v>126051559</v>
       </c>
       <c r="B14" t="n">
-        <v>98456</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>535458</v>
+        <v>535369</v>
       </c>
       <c r="R14" t="n">
-        <v>6722324</v>
+        <v>6722495</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2089,7 +2090,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2100,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2108,7 +2109,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126054200</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126054738</v>
       </c>
       <c r="B4" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>126051392</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>126050897</v>
       </c>
       <c r="B6" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,32 +1244,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126370901</v>
+        <v>126371162</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535355</v>
+        <v>535354</v>
       </c>
       <c r="R7" t="n">
-        <v>6722318</v>
+        <v>6722340</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,32 +1351,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126371162</v>
+        <v>126370901</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1386,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535354</v>
+        <v>535355</v>
       </c>
       <c r="R8" t="n">
-        <v>6722340</v>
+        <v>6722318</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,7 +1461,7 @@
         <v>126370532</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>126053829</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>126051147</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>126053644</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,64 +1896,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126053951</v>
+        <v>126051559</v>
       </c>
       <c r="B13" t="n">
-        <v>98459</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535458</v>
+        <v>535369</v>
       </c>
       <c r="R13" t="n">
-        <v>6722324</v>
+        <v>6722495</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1982,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,7 +1985,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2013,55 +1996,71 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126051559</v>
+        <v>126053951</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>98467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>535369</v>
+        <v>535458</v>
       </c>
       <c r="R14" t="n">
-        <v>6722495</v>
+        <v>6722324</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2090,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2100,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,6 +2108,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2237,7 +2237,7 @@
         <v>129090798</v>
       </c>
       <c r="B16" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2355,6 +2355,579 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129098263</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92816</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Jungfruberget 2, Jungfruberget 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>535428</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6722365</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>7 från i år och 7 fjolårs</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129116071</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57883</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>535283</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6722313</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129100061</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92816</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Jungfruberget 2, Jungfruberget 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>535422</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6722509</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Minst 13, både årets och fjolårets fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129115043</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58153</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>535199</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6722263</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129098432</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Jungfruberget 2, Jungfruberget 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>535452</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6722374</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -2237,7 +2237,7 @@
         <v>129090798</v>
       </c>
       <c r="B16" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>129098263</v>
       </c>
       <c r="B17" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,49 +2470,56 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129116071</v>
+        <v>129100061</v>
       </c>
       <c r="B18" t="n">
-        <v>57883</v>
+        <v>92819</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Jungfruberget 2, Jungfruberget 2, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535283</v>
+        <v>535422</v>
       </c>
       <c r="R18" t="n">
-        <v>6722313</v>
+        <v>6722509</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2539,22 +2546,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Minst 13, både årets och fjolårets fruktkroppar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2563,6 +2575,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2574,63 +2587,56 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129100061</v>
+        <v>129116071</v>
       </c>
       <c r="B19" t="n">
-        <v>92816</v>
+        <v>57883</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Jungfruberget 2, Jungfruberget 2, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>535422</v>
+        <v>535283</v>
       </c>
       <c r="R19" t="n">
-        <v>6722509</v>
+        <v>6722313</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2657,27 +2663,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:27</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Minst 13, både årets och fjolårets fruktkroppar</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2686,7 +2687,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -2237,7 +2237,7 @@
         <v>129090798</v>
       </c>
       <c r="B16" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>129098263</v>
       </c>
       <c r="B17" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>129100061</v>
       </c>
       <c r="B18" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>129116071</v>
       </c>
       <c r="B19" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>129115043</v>
       </c>
       <c r="B20" t="n">
-        <v>58153</v>
+        <v>58155</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>129098432</v>
       </c>
       <c r="B21" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -2237,7 +2237,7 @@
         <v>129090798</v>
       </c>
       <c r="B16" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>129098263</v>
       </c>
       <c r="B17" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,56 +2470,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129100061</v>
+        <v>129116071</v>
       </c>
       <c r="B18" t="n">
-        <v>92826</v>
+        <v>57885</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jungfruberget 2, Jungfruberget 2, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535422</v>
+        <v>535283</v>
       </c>
       <c r="R18" t="n">
-        <v>6722509</v>
+        <v>6722313</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2546,27 +2539,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:27</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Minst 13, både årets och fjolårets fruktkroppar</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2575,7 +2563,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2587,56 +2574,63 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129116071</v>
+        <v>129100061</v>
       </c>
       <c r="B19" t="n">
-        <v>57885</v>
+        <v>92833</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Jungfruberget 2, Jungfruberget 2, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>535283</v>
+        <v>535422</v>
       </c>
       <c r="R19" t="n">
-        <v>6722313</v>
+        <v>6722509</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2663,22 +2657,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Minst 13, både årets och fjolårets fruktkroppar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2687,6 +2686,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -2237,7 +2237,7 @@
         <v>129090798</v>
       </c>
       <c r="B16" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>129098263</v>
       </c>
       <c r="B17" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,49 +2470,56 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129116071</v>
+        <v>129100061</v>
       </c>
       <c r="B18" t="n">
-        <v>57885</v>
+        <v>92835</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Jungfruberget 2, Jungfruberget 2, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535283</v>
+        <v>535422</v>
       </c>
       <c r="R18" t="n">
-        <v>6722313</v>
+        <v>6722509</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2539,22 +2546,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Minst 13, både årets och fjolårets fruktkroppar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2563,6 +2575,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2574,63 +2587,56 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129100061</v>
+        <v>129116071</v>
       </c>
       <c r="B19" t="n">
-        <v>92833</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Jungfruberget 2, Jungfruberget 2, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>535422</v>
+        <v>535283</v>
       </c>
       <c r="R19" t="n">
-        <v>6722509</v>
+        <v>6722313</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2657,27 +2663,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:27</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Minst 13, både årets och fjolårets fruktkroppar</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2686,7 +2687,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2708,7 +2708,7 @@
         <v>129115043</v>
       </c>
       <c r="B20" t="n">
-        <v>58155</v>
+        <v>58157</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>129098432</v>
       </c>
       <c r="B21" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -2237,7 +2237,7 @@
         <v>129090798</v>
       </c>
       <c r="B16" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>129098263</v>
       </c>
       <c r="B17" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>129100061</v>
       </c>
       <c r="B18" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -2237,7 +2237,7 @@
         <v>129090798</v>
       </c>
       <c r="B16" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>129098263</v>
       </c>
       <c r="B17" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>129100061</v>
       </c>
       <c r="B18" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -2237,7 +2237,7 @@
         <v>129090798</v>
       </c>
       <c r="B16" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>129098263</v>
       </c>
       <c r="B17" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>129100061</v>
       </c>
       <c r="B18" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -2237,7 +2237,7 @@
         <v>129090798</v>
       </c>
       <c r="B16" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>129098263</v>
       </c>
       <c r="B17" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>129100061</v>
       </c>
       <c r="B18" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -2237,7 +2237,7 @@
         <v>129090798</v>
       </c>
       <c r="B16" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>129098263</v>
       </c>
       <c r="B17" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,56 +2470,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129100061</v>
+        <v>129116071</v>
       </c>
       <c r="B18" t="n">
-        <v>92827</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jungfruberget 2, Jungfruberget 2, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535422</v>
+        <v>535283</v>
       </c>
       <c r="R18" t="n">
-        <v>6722509</v>
+        <v>6722313</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2546,27 +2539,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:27</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Minst 13, både årets och fjolårets fruktkroppar</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2575,7 +2563,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2587,56 +2574,63 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129116071</v>
+        <v>129100061</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>92831</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Jungfruberget 2, Jungfruberget 2, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>535283</v>
+        <v>535422</v>
       </c>
       <c r="R19" t="n">
-        <v>6722313</v>
+        <v>6722509</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2663,22 +2657,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Minst 13, både årets och fjolårets fruktkroppar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2687,6 +2686,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -2237,7 +2237,7 @@
         <v>129090798</v>
       </c>
       <c r="B16" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>129098263</v>
       </c>
       <c r="B17" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,49 +2470,56 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129116071</v>
+        <v>129100061</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>92832</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Jungfruberget 2, Jungfruberget 2, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535283</v>
+        <v>535422</v>
       </c>
       <c r="R18" t="n">
-        <v>6722313</v>
+        <v>6722509</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2539,22 +2546,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Minst 13, både årets och fjolårets fruktkroppar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2563,6 +2575,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2574,63 +2587,56 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129100061</v>
+        <v>129116071</v>
       </c>
       <c r="B19" t="n">
-        <v>92831</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Jungfruberget 2, Jungfruberget 2, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>535422</v>
+        <v>535283</v>
       </c>
       <c r="R19" t="n">
-        <v>6722509</v>
+        <v>6722313</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2657,27 +2663,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:27</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Minst 13, både årets och fjolårets fruktkroppar</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2686,7 +2687,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -2470,56 +2470,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129100061</v>
+        <v>129116071</v>
       </c>
       <c r="B18" t="n">
-        <v>92832</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jungfruberget 2, Jungfruberget 2, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535422</v>
+        <v>535283</v>
       </c>
       <c r="R18" t="n">
-        <v>6722509</v>
+        <v>6722313</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2546,27 +2539,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:27</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Minst 13, både årets och fjolårets fruktkroppar</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2575,7 +2563,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2587,56 +2574,63 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129116071</v>
+        <v>129100061</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>92832</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Jungfruberget 2, Jungfruberget 2, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>535283</v>
+        <v>535422</v>
       </c>
       <c r="R19" t="n">
-        <v>6722313</v>
+        <v>6722509</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2663,22 +2657,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Minst 13, både årets och fjolårets fruktkroppar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2687,6 +2686,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -2237,7 +2237,7 @@
         <v>129090798</v>
       </c>
       <c r="B16" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>129098263</v>
       </c>
       <c r="B17" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,49 +2470,56 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129116071</v>
+        <v>129100061</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>92835</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Jungfruberget 2, Jungfruberget 2, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535283</v>
+        <v>535422</v>
       </c>
       <c r="R18" t="n">
-        <v>6722313</v>
+        <v>6722509</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2539,22 +2546,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Minst 13, både årets och fjolårets fruktkroppar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2563,6 +2575,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2574,63 +2587,56 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129100061</v>
+        <v>129116071</v>
       </c>
       <c r="B19" t="n">
-        <v>92832</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Jungfruberget 2, Jungfruberget 2, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>535422</v>
+        <v>535283</v>
       </c>
       <c r="R19" t="n">
-        <v>6722509</v>
+        <v>6722313</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2657,27 +2663,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:27</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Minst 13, både årets och fjolårets fruktkroppar</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2686,7 +2687,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -2361,7 +2361,7 @@
         <v>129098263</v>
       </c>
       <c r="B17" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>129100061</v>
       </c>
       <c r="B18" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>129116071</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>129115043</v>
       </c>
       <c r="B20" t="n">
-        <v>58157</v>
+        <v>58160</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>129098432</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2929,6 +2929,113 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129688736</v>
+      </c>
+      <c r="B22" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Högtäkt, Högtäkt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>535536</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6722396</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Ulf Magnusson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ulf Magnusson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3036,6 +3036,237 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129703661</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92907</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>535375</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6722429</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129704155</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>535272</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6722342</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -3041,7 +3041,7 @@
         <v>129703661</v>
       </c>
       <c r="B23" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>129704155</v>
       </c>
       <c r="B24" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -3041,7 +3041,7 @@
         <v>129703661</v>
       </c>
       <c r="B23" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -3041,7 +3041,7 @@
         <v>129703661</v>
       </c>
       <c r="B23" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -3041,7 +3041,7 @@
         <v>129703661</v>
       </c>
       <c r="B23" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -3157,7 +3157,7 @@
         <v>129704155</v>
       </c>
       <c r="B24" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -3041,7 +3041,7 @@
         <v>129703661</v>
       </c>
       <c r="B23" t="n">
-        <v>92919</v>
+        <v>92922</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2934,7 +2934,7 @@
         <v>129688736</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>129703661</v>
       </c>
       <c r="B23" t="n">
-        <v>92922</v>
+        <v>92925</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>129704155</v>
       </c>
       <c r="B24" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3266,6 +3266,240 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129865280</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Jungfruberget östra, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>535504</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6722415</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129863936</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57866</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103035</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Corvus corone</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Jungfruberget östra, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>535285</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6722314</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -3041,7 +3041,7 @@
         <v>129703661</v>
       </c>
       <c r="B23" t="n">
-        <v>92925</v>
+        <v>92926</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -3041,7 +3041,7 @@
         <v>129703661</v>
       </c>
       <c r="B23" t="n">
-        <v>92926</v>
+        <v>92943</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>129863936</v>
       </c>
       <c r="B26" t="n">
-        <v>57866</v>
+        <v>57867</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -3503,45 +3503,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130164260</v>
+        <v>130163497</v>
       </c>
       <c r="B27" t="n">
-        <v>8451</v>
+        <v>57738</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>535322</v>
+        <v>535512</v>
       </c>
       <c r="R27" t="n">
-        <v>6722412</v>
+        <v>6722482</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3610,45 +3610,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130163497</v>
+        <v>130164260</v>
       </c>
       <c r="B28" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Jungfruberget, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>535512</v>
+        <v>535322</v>
       </c>
       <c r="R28" t="n">
-        <v>6722482</v>
+        <v>6722412</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126054200</v>
+        <v>126370384</v>
       </c>
       <c r="B2" t="n">
-        <v>57669</v>
+        <v>8447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Högtäkt, Högtäkt, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535583</v>
+        <v>535401</v>
       </c>
       <c r="R2" t="n">
-        <v>6722243</v>
+        <v>6722359</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,55 +775,55 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126370384</v>
+        <v>126054200</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>57654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Högtäkt, Högtäkt, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535401</v>
+        <v>535583</v>
       </c>
       <c r="R3" t="n">
-        <v>6722359</v>
+        <v>6722243</v>
       </c>
       <c r="S3" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -892,7 +892,7 @@
         <v>126054738</v>
       </c>
       <c r="B4" t="n">
-        <v>98384</v>
+        <v>98353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>126051392</v>
       </c>
       <c r="B5" t="n">
-        <v>57669</v>
+        <v>57654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>126050897</v>
       </c>
       <c r="B6" t="n">
-        <v>56864</v>
+        <v>56849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,32 +1244,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126371162</v>
+        <v>126370901</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>57654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535354</v>
+        <v>535355</v>
       </c>
       <c r="R7" t="n">
-        <v>6722340</v>
+        <v>6722318</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,32 +1351,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126370901</v>
+        <v>126371162</v>
       </c>
       <c r="B8" t="n">
-        <v>57669</v>
+        <v>8447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1386,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535355</v>
+        <v>535354</v>
       </c>
       <c r="R8" t="n">
-        <v>6722318</v>
+        <v>6722340</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,7 +1461,7 @@
         <v>126370532</v>
       </c>
       <c r="B9" t="n">
-        <v>57669</v>
+        <v>57654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>126053829</v>
       </c>
       <c r="B10" t="n">
-        <v>57669</v>
+        <v>57654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>126051147</v>
       </c>
       <c r="B11" t="n">
-        <v>57669</v>
+        <v>57654</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>126053644</v>
       </c>
       <c r="B12" t="n">
-        <v>57669</v>
+        <v>57654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>126051559</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>8447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>126053951</v>
       </c>
       <c r="B14" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>126372830</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>8447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>129865280</v>
       </c>
       <c r="B25" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>129863936</v>
       </c>
       <c r="B26" t="n">
-        <v>57868</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>130163497</v>
       </c>
       <c r="B27" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -3503,45 +3503,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130163497</v>
+        <v>130164260</v>
       </c>
       <c r="B27" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Jungfruberget, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>535512</v>
+        <v>535322</v>
       </c>
       <c r="R27" t="n">
-        <v>6722482</v>
+        <v>6722412</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3610,45 +3610,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130164260</v>
+        <v>130163497</v>
       </c>
       <c r="B28" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>535322</v>
+        <v>535512</v>
       </c>
       <c r="R28" t="n">
-        <v>6722412</v>
+        <v>6722482</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126370384</v>
+        <v>126054200</v>
       </c>
       <c r="B2" t="n">
-        <v>8447</v>
+        <v>57669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Högtäkt, Högtäkt, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535401</v>
+        <v>535583</v>
       </c>
       <c r="R2" t="n">
-        <v>6722359</v>
+        <v>6722243</v>
       </c>
       <c r="S2" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,55 +775,55 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126054200</v>
+        <v>126370384</v>
       </c>
       <c r="B3" t="n">
-        <v>57654</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högtäkt, Högtäkt, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535583</v>
+        <v>535401</v>
       </c>
       <c r="R3" t="n">
-        <v>6722243</v>
+        <v>6722359</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -892,7 +892,7 @@
         <v>126054738</v>
       </c>
       <c r="B4" t="n">
-        <v>98353</v>
+        <v>98384</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>126051392</v>
       </c>
       <c r="B5" t="n">
-        <v>57654</v>
+        <v>57669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>126050897</v>
       </c>
       <c r="B6" t="n">
-        <v>56849</v>
+        <v>56864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,32 +1244,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126370901</v>
+        <v>126371162</v>
       </c>
       <c r="B7" t="n">
-        <v>57654</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535355</v>
+        <v>535354</v>
       </c>
       <c r="R7" t="n">
-        <v>6722318</v>
+        <v>6722340</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,32 +1351,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126371162</v>
+        <v>126370901</v>
       </c>
       <c r="B8" t="n">
-        <v>8447</v>
+        <v>57669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1386,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535354</v>
+        <v>535355</v>
       </c>
       <c r="R8" t="n">
-        <v>6722340</v>
+        <v>6722318</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,7 +1461,7 @@
         <v>126370532</v>
       </c>
       <c r="B9" t="n">
-        <v>57654</v>
+        <v>57669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>126053829</v>
       </c>
       <c r="B10" t="n">
-        <v>57654</v>
+        <v>57669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>126051147</v>
       </c>
       <c r="B11" t="n">
-        <v>57654</v>
+        <v>57669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>126053644</v>
       </c>
       <c r="B12" t="n">
-        <v>57654</v>
+        <v>57669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>126051559</v>
       </c>
       <c r="B13" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>126053951</v>
       </c>
       <c r="B14" t="n">
-        <v>98436</v>
+        <v>98467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>126372830</v>
       </c>
       <c r="B15" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3503,45 +3503,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130164260</v>
+        <v>130163497</v>
       </c>
       <c r="B27" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>535322</v>
+        <v>535512</v>
       </c>
       <c r="R27" t="n">
-        <v>6722412</v>
+        <v>6722482</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3610,45 +3610,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130163497</v>
+        <v>130164260</v>
       </c>
       <c r="B28" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Jungfruberget, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>535512</v>
+        <v>535322</v>
       </c>
       <c r="R28" t="n">
-        <v>6722482</v>
+        <v>6722412</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -3506,7 +3506,7 @@
         <v>130163497</v>
       </c>
       <c r="B27" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -3506,7 +3506,7 @@
         <v>130163497</v>
       </c>
       <c r="B27" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3715,6 +3715,1171 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131939733</v>
+      </c>
+      <c r="B29" t="n">
+        <v>93127</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Jungfruberget 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>535434</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6722503</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131939966</v>
+      </c>
+      <c r="B30" t="n">
+        <v>8454</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Jungfruberget 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>535378</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6722481</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131939942</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Jungfruberget 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>535387</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6722492</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131939773</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Jungfruberget 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>535462</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6722514</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>födosöks hack</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131939888</v>
+      </c>
+      <c r="B33" t="n">
+        <v>93127</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Jungfruberget 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>535399</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6722505</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>130053440</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58277</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Jungfruberget 2, Jungfruberget 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>535384</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6722509</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>131939790</v>
+      </c>
+      <c r="B35" t="n">
+        <v>8454</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Jungfruberget 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>535449</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6722509</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>131939876</v>
+      </c>
+      <c r="B36" t="n">
+        <v>93127</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Jungfruberget 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>535389</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6722514</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>131939924</v>
+      </c>
+      <c r="B37" t="n">
+        <v>93127</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Jungfruberget 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>535402</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6722499</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>131939837</v>
+      </c>
+      <c r="B38" t="n">
+        <v>8454</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Jungfruberget 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>535425</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6722501</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -3717,10 +3717,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131939733</v>
+        <v>131939966</v>
       </c>
       <c r="B29" t="n">
-        <v>93127</v>
+        <v>8455</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3728,26 +3728,28 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3755,10 +3757,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>535434</v>
+        <v>535378</v>
       </c>
       <c r="R29" t="n">
-        <v>6722503</v>
+        <v>6722481</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3790,7 +3792,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3800,7 +3802,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3824,14 +3826,18 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131939966</v>
+        <v>131939733</v>
       </c>
       <c r="B30" t="n">
-        <v>8454</v>
+        <v>93129</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3839,28 +3845,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3868,10 +3872,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>535378</v>
+        <v>535434</v>
       </c>
       <c r="R30" t="n">
-        <v>6722481</v>
+        <v>6722503</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3903,7 +3907,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3913,7 +3917,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3937,18 +3941,14 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>131939942</v>
       </c>
       <c r="B31" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>131939773</v>
       </c>
       <c r="B32" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>131939888</v>
       </c>
       <c r="B33" t="n">
-        <v>93127</v>
+        <v>93129</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>130053440</v>
       </c>
       <c r="B34" t="n">
-        <v>58277</v>
+        <v>58279</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>131939790</v>
       </c>
       <c r="B35" t="n">
-        <v>8454</v>
+        <v>8455</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>131939876</v>
       </c>
       <c r="B36" t="n">
-        <v>93127</v>
+        <v>93129</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4646,10 +4646,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131939924</v>
+        <v>131939837</v>
       </c>
       <c r="B37" t="n">
-        <v>93127</v>
+        <v>8455</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4657,34 +4657,28 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4692,10 +4686,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>535402</v>
+        <v>535425</v>
       </c>
       <c r="R37" t="n">
-        <v>6722499</v>
+        <v>6722501</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4727,7 +4721,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4737,7 +4731,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4761,18 +4755,14 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131939837</v>
+        <v>131939924</v>
       </c>
       <c r="B38" t="n">
-        <v>8454</v>
+        <v>93129</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4780,28 +4770,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4809,10 +4805,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>535425</v>
+        <v>535402</v>
       </c>
       <c r="R38" t="n">
-        <v>6722501</v>
+        <v>6722499</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4844,7 +4840,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4854,7 +4850,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4878,7 +4874,11 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -3717,10 +3717,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131939966</v>
+        <v>131939733</v>
       </c>
       <c r="B29" t="n">
-        <v>8455</v>
+        <v>93134</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3728,28 +3728,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3757,10 +3755,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>535378</v>
+        <v>535434</v>
       </c>
       <c r="R29" t="n">
-        <v>6722481</v>
+        <v>6722503</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3792,7 +3790,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3802,7 +3800,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3826,18 +3824,14 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131939733</v>
+        <v>131939966</v>
       </c>
       <c r="B30" t="n">
-        <v>93129</v>
+        <v>8455</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,26 +3839,28 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3872,10 +3868,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>535434</v>
+        <v>535378</v>
       </c>
       <c r="R30" t="n">
-        <v>6722503</v>
+        <v>6722481</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3907,7 +3903,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3917,7 +3913,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3941,14 +3937,18 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>131939942</v>
       </c>
       <c r="B31" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>131939773</v>
       </c>
       <c r="B32" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>131939888</v>
       </c>
       <c r="B33" t="n">
-        <v>93129</v>
+        <v>93134</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>130053440</v>
       </c>
       <c r="B34" t="n">
-        <v>58279</v>
+        <v>58284</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>131939876</v>
       </c>
       <c r="B36" t="n">
-        <v>93129</v>
+        <v>93134</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4646,10 +4646,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131939837</v>
+        <v>131939924</v>
       </c>
       <c r="B37" t="n">
-        <v>8455</v>
+        <v>93134</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4657,28 +4657,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4686,10 +4692,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>535425</v>
+        <v>535402</v>
       </c>
       <c r="R37" t="n">
-        <v>6722501</v>
+        <v>6722499</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4721,7 +4727,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4731,7 +4737,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4755,14 +4761,18 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131939924</v>
+        <v>131939837</v>
       </c>
       <c r="B38" t="n">
-        <v>93129</v>
+        <v>8455</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4770,34 +4780,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4805,10 +4809,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>535402</v>
+        <v>535425</v>
       </c>
       <c r="R38" t="n">
-        <v>6722499</v>
+        <v>6722501</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4840,7 +4844,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4850,7 +4854,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4874,11 +4878,7 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -3717,10 +3717,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131939733</v>
+        <v>131939966</v>
       </c>
       <c r="B29" t="n">
-        <v>93134</v>
+        <v>8455</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3728,26 +3728,28 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3755,10 +3757,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>535434</v>
+        <v>535378</v>
       </c>
       <c r="R29" t="n">
-        <v>6722503</v>
+        <v>6722481</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3790,7 +3792,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3800,7 +3802,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3824,14 +3826,18 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131939966</v>
+        <v>131939733</v>
       </c>
       <c r="B30" t="n">
-        <v>8455</v>
+        <v>93134</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3839,28 +3845,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3868,10 +3872,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>535378</v>
+        <v>535434</v>
       </c>
       <c r="R30" t="n">
-        <v>6722481</v>
+        <v>6722503</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3903,7 +3907,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3913,7 +3917,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3937,11 +3941,7 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -3720,7 +3720,7 @@
         <v>131939733</v>
       </c>
       <c r="B29" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>131939888</v>
       </c>
       <c r="B33" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>130053440</v>
       </c>
       <c r="B34" t="n">
-        <v>58320</v>
+        <v>58322</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>131939876</v>
       </c>
       <c r="B36" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4646,10 +4646,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131939924</v>
+        <v>131939837</v>
       </c>
       <c r="B37" t="n">
-        <v>93177</v>
+        <v>8455</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4657,34 +4657,28 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4692,10 +4686,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>535402</v>
+        <v>535425</v>
       </c>
       <c r="R37" t="n">
-        <v>6722499</v>
+        <v>6722501</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4727,7 +4721,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4737,7 +4731,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4761,18 +4755,14 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131939837</v>
+        <v>131939924</v>
       </c>
       <c r="B38" t="n">
-        <v>8455</v>
+        <v>93180</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4780,28 +4770,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4809,10 +4805,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>535425</v>
+        <v>535402</v>
       </c>
       <c r="R38" t="n">
-        <v>6722501</v>
+        <v>6722499</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4844,7 +4840,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4854,7 +4850,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4878,7 +4874,11 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -4646,10 +4646,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131939837</v>
+        <v>131939924</v>
       </c>
       <c r="B37" t="n">
-        <v>8455</v>
+        <v>93180</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4657,28 +4657,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4686,10 +4692,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>535425</v>
+        <v>535402</v>
       </c>
       <c r="R37" t="n">
-        <v>6722501</v>
+        <v>6722499</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4721,7 +4727,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4731,7 +4737,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4755,14 +4761,18 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131939924</v>
+        <v>131939837</v>
       </c>
       <c r="B38" t="n">
-        <v>93180</v>
+        <v>8455</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4770,34 +4780,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4805,10 +4809,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>535402</v>
+        <v>535425</v>
       </c>
       <c r="R38" t="n">
-        <v>6722499</v>
+        <v>6722501</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4840,7 +4844,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4850,7 +4854,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4874,11 +4878,7 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -4646,10 +4646,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131939924</v>
+        <v>131939837</v>
       </c>
       <c r="B37" t="n">
-        <v>93180</v>
+        <v>8455</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4657,34 +4657,28 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4692,10 +4686,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>535402</v>
+        <v>535425</v>
       </c>
       <c r="R37" t="n">
-        <v>6722499</v>
+        <v>6722501</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4727,7 +4721,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4737,7 +4731,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4761,18 +4755,14 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131939837</v>
+        <v>131939924</v>
       </c>
       <c r="B38" t="n">
-        <v>8455</v>
+        <v>93180</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4780,28 +4770,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4809,10 +4805,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>535425</v>
+        <v>535402</v>
       </c>
       <c r="R38" t="n">
-        <v>6722501</v>
+        <v>6722499</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4844,7 +4840,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4854,7 +4850,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4878,7 +4874,11 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -3945,7 +3945,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131939942</v>
+        <v>131939773</v>
       </c>
       <c r="B31" t="n">
         <v>57945</v>
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>535387</v>
+        <v>535462</v>
       </c>
       <c r="R31" t="n">
-        <v>6722492</v>
+        <v>6722514</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4033,7 +4033,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>födosöks hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4056,15 +4061,11 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131939773</v>
+        <v>131939942</v>
       </c>
       <c r="B32" t="n">
         <v>57945</v>
@@ -4107,10 +4108,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>535462</v>
+        <v>535387</v>
       </c>
       <c r="R32" t="n">
-        <v>6722514</v>
+        <v>6722492</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4142,7 +4143,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4152,12 +4153,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:47</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>födosöks hack</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4180,7 +4176,11 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4646,10 +4646,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131939837</v>
+        <v>131939924</v>
       </c>
       <c r="B37" t="n">
-        <v>8455</v>
+        <v>93180</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4657,28 +4657,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4686,10 +4692,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>535425</v>
+        <v>535402</v>
       </c>
       <c r="R37" t="n">
-        <v>6722501</v>
+        <v>6722499</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4721,7 +4727,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4731,7 +4737,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4755,14 +4761,18 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131939924</v>
+        <v>131939837</v>
       </c>
       <c r="B38" t="n">
-        <v>93180</v>
+        <v>8455</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4770,34 +4780,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4805,10 +4809,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>535402</v>
+        <v>535425</v>
       </c>
       <c r="R38" t="n">
-        <v>6722499</v>
+        <v>6722501</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4840,7 +4844,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4850,7 +4854,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4874,11 +4878,7 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -3717,10 +3717,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131939733</v>
+        <v>131939966</v>
       </c>
       <c r="B29" t="n">
-        <v>93180</v>
+        <v>8455</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3728,26 +3728,28 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3755,10 +3757,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>535434</v>
+        <v>535378</v>
       </c>
       <c r="R29" t="n">
-        <v>6722503</v>
+        <v>6722481</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3790,7 +3792,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3800,7 +3802,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3824,14 +3826,18 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131939966</v>
+        <v>131939733</v>
       </c>
       <c r="B30" t="n">
-        <v>8455</v>
+        <v>93180</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3839,28 +3845,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3868,10 +3872,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>535378</v>
+        <v>535434</v>
       </c>
       <c r="R30" t="n">
-        <v>6722481</v>
+        <v>6722503</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3903,7 +3907,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3913,7 +3917,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3937,11 +3941,7 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -3717,10 +3717,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131939966</v>
+        <v>131939733</v>
       </c>
       <c r="B29" t="n">
-        <v>8455</v>
+        <v>93186</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3728,28 +3728,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3757,10 +3755,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>535378</v>
+        <v>535434</v>
       </c>
       <c r="R29" t="n">
-        <v>6722481</v>
+        <v>6722503</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3792,7 +3790,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3802,7 +3800,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3826,18 +3824,14 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131939733</v>
+        <v>131939966</v>
       </c>
       <c r="B30" t="n">
-        <v>93180</v>
+        <v>8455</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,26 +3839,28 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3872,10 +3868,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>535434</v>
+        <v>535378</v>
       </c>
       <c r="R30" t="n">
-        <v>6722503</v>
+        <v>6722481</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3907,7 +3903,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3917,7 +3913,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3941,14 +3937,18 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131939773</v>
+        <v>131939942</v>
       </c>
       <c r="B31" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>535462</v>
+        <v>535387</v>
       </c>
       <c r="R31" t="n">
-        <v>6722514</v>
+        <v>6722492</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4033,12 +4033,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:47</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>födosöks hack</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4061,14 +4056,18 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131939942</v>
+        <v>131939773</v>
       </c>
       <c r="B32" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4108,10 +4107,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>535387</v>
+        <v>535462</v>
       </c>
       <c r="R32" t="n">
-        <v>6722492</v>
+        <v>6722514</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4143,7 +4142,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4153,7 +4152,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>födosöks hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4176,18 +4180,14 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>131939888</v>
       </c>
       <c r="B33" t="n">
-        <v>93180</v>
+        <v>93186</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>130053440</v>
       </c>
       <c r="B34" t="n">
-        <v>58322</v>
+        <v>58323</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>131939876</v>
       </c>
       <c r="B36" t="n">
-        <v>93180</v>
+        <v>93186</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4646,10 +4646,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131939924</v>
+        <v>131939837</v>
       </c>
       <c r="B37" t="n">
-        <v>93180</v>
+        <v>8455</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4657,34 +4657,28 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4692,10 +4686,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>535402</v>
+        <v>535425</v>
       </c>
       <c r="R37" t="n">
-        <v>6722499</v>
+        <v>6722501</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4727,7 +4721,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4737,7 +4731,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4761,18 +4755,14 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131939837</v>
+        <v>131939924</v>
       </c>
       <c r="B38" t="n">
-        <v>8455</v>
+        <v>93186</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4780,28 +4770,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4809,10 +4805,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>535425</v>
+        <v>535402</v>
       </c>
       <c r="R38" t="n">
-        <v>6722501</v>
+        <v>6722499</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4844,7 +4840,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4854,7 +4850,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4878,7 +4874,11 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -4646,10 +4646,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131939837</v>
+        <v>131939924</v>
       </c>
       <c r="B37" t="n">
-        <v>8455</v>
+        <v>93186</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4657,28 +4657,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4686,10 +4692,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>535425</v>
+        <v>535402</v>
       </c>
       <c r="R37" t="n">
-        <v>6722501</v>
+        <v>6722499</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4721,7 +4727,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4731,7 +4737,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4755,14 +4761,18 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131939924</v>
+        <v>131939837</v>
       </c>
       <c r="B38" t="n">
-        <v>93186</v>
+        <v>8455</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4770,34 +4780,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4805,10 +4809,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>535402</v>
+        <v>535425</v>
       </c>
       <c r="R38" t="n">
-        <v>6722499</v>
+        <v>6722501</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4840,7 +4844,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4850,7 +4854,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4874,11 +4878,7 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -3720,7 +3720,7 @@
         <v>131939733</v>
       </c>
       <c r="B29" t="n">
-        <v>93186</v>
+        <v>93196</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>131939942</v>
       </c>
       <c r="B31" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>131939773</v>
       </c>
       <c r="B32" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>131939888</v>
       </c>
       <c r="B33" t="n">
-        <v>93186</v>
+        <v>93196</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>130053440</v>
       </c>
       <c r="B34" t="n">
-        <v>58323</v>
+        <v>58327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>131939876</v>
       </c>
       <c r="B36" t="n">
-        <v>93186</v>
+        <v>93196</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>131939924</v>
       </c>
       <c r="B37" t="n">
-        <v>93186</v>
+        <v>93196</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -4187,7 +4187,7 @@
         <v>131939888</v>
       </c>
       <c r="B33" t="n">
-        <v>93257</v>
+        <v>93264</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>131939876</v>
       </c>
       <c r="B36" t="n">
-        <v>93257</v>
+        <v>93264</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>131939924</v>
       </c>
       <c r="B37" t="n">
-        <v>93257</v>
+        <v>93264</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126054200</v>
+        <v>129098263</v>
       </c>
       <c r="B2" t="n">
-        <v>57669</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Högtäkt, Högtäkt, Dlr</t>
+          <t>Jungfruberget 2, Jungfruberget 2, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535583</v>
+        <v>535428</v>
       </c>
       <c r="R2" t="n">
-        <v>6722243</v>
+        <v>6722365</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,22 +740,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>7 från i år och 7 fjolårs</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,55 +780,66 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126370384</v>
+        <v>129100061</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Jungfruberget 2, Jungfruberget 2, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535401</v>
+        <v>535422</v>
       </c>
       <c r="R3" t="n">
-        <v>6722359</v>
+        <v>6722509</v>
       </c>
       <c r="S3" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,22 +863,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Minst 13, både årets och fjolårets fruktkroppar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,6 +892,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,62 +911,62 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126054738</v>
+        <v>130037365</v>
       </c>
       <c r="B4" t="n">
-        <v>98384</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Urfjällsgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535311</v>
+        <v>535491</v>
       </c>
       <c r="R4" t="n">
-        <v>6722256</v>
+        <v>6722529</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,27 +990,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:46</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Blom eller knopp</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,22 +1020,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126051392</v>
+        <v>131939733</v>
       </c>
       <c r="B5" t="n">
-        <v>57669</v>
+        <v>93271</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,39 +1043,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Jungfruberget 2, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535382</v>
+        <v>535434</v>
       </c>
       <c r="R5" t="n">
-        <v>6722489</v>
+        <v>6722503</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,22 +1100,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,6 +1124,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1127,50 +1143,52 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126050897</v>
+        <v>131939876</v>
       </c>
       <c r="B6" t="n">
-        <v>56864</v>
+        <v>93271</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Jungfruberget 2, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535233</v>
+        <v>535389</v>
       </c>
       <c r="R6" t="n">
-        <v>6722467</v>
+        <v>6722514</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,27 +1215,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På hranstubbe</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,6 +1239,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1237,52 +1251,67 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126371162</v>
+        <v>131939888</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>93271</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Jungfruberget 2, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535354</v>
+        <v>535399</v>
       </c>
       <c r="R7" t="n">
-        <v>6722340</v>
+        <v>6722505</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,22 +1338,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,6 +1362,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1347,14 +1377,18 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126370901</v>
+        <v>131939924</v>
       </c>
       <c r="B8" t="n">
-        <v>57669</v>
+        <v>93271</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,34 +1396,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Jungfruberget 2, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535355</v>
+        <v>535402</v>
       </c>
       <c r="R8" t="n">
-        <v>6722318</v>
+        <v>6722499</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,22 +1461,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1440,6 +1485,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1454,14 +1500,18 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126370532</v>
+        <v>129090798</v>
       </c>
       <c r="B9" t="n">
-        <v>57669</v>
+        <v>93235</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,37 +1519,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Jungfruberget 2, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535396</v>
+        <v>535497</v>
       </c>
       <c r="R9" t="n">
-        <v>6722329</v>
+        <v>6722448</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1523,22 +1584,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>två hattar var ca 25cm i diameter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1547,6 +1613,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1565,10 +1632,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126053829</v>
+        <v>129702227</v>
       </c>
       <c r="B10" t="n">
-        <v>57669</v>
+        <v>93235</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,34 +1643,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Högtäkt, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535454</v>
+        <v>535645</v>
       </c>
       <c r="R10" t="n">
-        <v>6722333</v>
+        <v>6722231</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,27 +1706,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:57</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hästmyra</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1665,22 +1736,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Ulf Magnusson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Ulf Magnusson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126051147</v>
+        <v>129703661</v>
       </c>
       <c r="B11" t="n">
-        <v>57669</v>
+        <v>93235</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,37 +1759,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535301</v>
+        <v>535375</v>
       </c>
       <c r="R11" t="n">
-        <v>6722491</v>
+        <v>6722429</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1742,22 +1822,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1772,22 +1852,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126053644</v>
+        <v>131939678</v>
       </c>
       <c r="B12" t="n">
-        <v>57669</v>
+        <v>93309</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,39 +1875,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Urfjällsgruvan, Urfjällsgruvan, Dlr</t>
+          <t>Jungfruberget 2, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535482</v>
+        <v>535474</v>
       </c>
       <c r="R12" t="n">
-        <v>6722442</v>
+        <v>6722540</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,22 +1932,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,6 +1956,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1896,10 +1975,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126051559</v>
+        <v>126051147</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,21 +1986,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1931,10 +2010,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535369</v>
+        <v>535301</v>
       </c>
       <c r="R13" t="n">
-        <v>6722495</v>
+        <v>6722491</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1966,7 +2045,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +2055,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,64 +2082,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126053951</v>
+        <v>126051392</v>
       </c>
       <c r="B14" t="n">
-        <v>98467</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>535458</v>
+        <v>535382</v>
       </c>
       <c r="R14" t="n">
-        <v>6722324</v>
+        <v>6722489</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2089,7 +2157,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2167,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2108,7 +2176,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2120,17 +2187,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126372830</v>
+        <v>126053644</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,34 +2205,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Urfjällsgruvan, Urfjällsgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>535212</v>
+        <v>535482</v>
       </c>
       <c r="R15" t="n">
-        <v>6722317</v>
+        <v>6722442</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2192,22 +2264,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:57</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>20:57</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2234,59 +2306,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129090798</v>
+        <v>126053829</v>
       </c>
       <c r="B16" t="n">
-        <v>92873</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Jungfruberget 2, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>535497</v>
+        <v>535454</v>
       </c>
       <c r="R16" t="n">
-        <v>6722448</v>
+        <v>6722333</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2310,27 +2371,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>två hattar var ca 25cm i diameter</t>
+          <t>Hästmyra</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2339,7 +2400,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2358,10 +2418,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129098263</v>
+        <v>126054200</v>
       </c>
       <c r="B17" t="n">
-        <v>92863</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2369,34 +2429,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Jungfruberget 2, Jungfruberget 2, Dlr</t>
+          <t>Högtäkt, Högtäkt, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>535428</v>
+        <v>535583</v>
       </c>
       <c r="R17" t="n">
-        <v>6722365</v>
+        <v>6722243</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2423,27 +2483,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>7 från i år och 7 fjolårs</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2463,17 +2518,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129100061</v>
+        <v>126370532</v>
       </c>
       <c r="B18" t="n">
-        <v>92863</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2481,45 +2536,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jungfruberget 2, Jungfruberget 2, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535422</v>
+        <v>535396</v>
       </c>
       <c r="R18" t="n">
-        <v>6722509</v>
+        <v>6722329</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2546,27 +2590,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:27</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Minst 13, både årets och fjolårets fruktkroppar</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2575,7 +2614,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2594,49 +2632,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129116071</v>
+        <v>126370901</v>
       </c>
       <c r="B19" t="n">
-        <v>57890</v>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>535283</v>
+        <v>535355</v>
       </c>
       <c r="R19" t="n">
-        <v>6722313</v>
+        <v>6722318</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2663,22 +2697,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2698,64 +2732,52 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129115043</v>
+        <v>129098432</v>
       </c>
       <c r="B20" t="n">
-        <v>58160</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Jungfruberget 2, Jungfruberget 2, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>535199</v>
+        <v>535452</v>
       </c>
       <c r="R20" t="n">
-        <v>6722263</v>
+        <v>6722374</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2782,22 +2804,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2824,14 +2846,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129098432</v>
+        <v>129688888</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2855,14 +2877,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Jungfruberget 2, Jungfruberget 2, Dlr</t>
+          <t>Högtäkt, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>535452</v>
+        <v>535645</v>
       </c>
       <c r="R21" t="n">
-        <v>6722374</v>
+        <v>6722231</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2889,22 +2911,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2919,22 +2941,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Ulf Magnusson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Ulf Magnusson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129688736</v>
+        <v>129704155</v>
       </c>
       <c r="B22" t="n">
-        <v>8451</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2942,34 +2964,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Högtäkt, Högtäkt, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>535536</v>
+        <v>535272</v>
       </c>
       <c r="R22" t="n">
-        <v>6722396</v>
+        <v>6722342</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2996,22 +3026,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3026,66 +3056,65 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulf Magnusson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulf Magnusson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129703661</v>
+        <v>129865280</v>
       </c>
       <c r="B23" t="n">
-        <v>92948</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Jungfruberget östra, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>535375</v>
+        <v>535504</v>
       </c>
       <c r="R23" t="n">
-        <v>6722429</v>
+        <v>6722415</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3112,22 +3141,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3142,26 +3171,26 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129704155</v>
+        <v>130163497</v>
       </c>
       <c r="B24" t="n">
-        <v>57737</v>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3183,24 +3212,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>535272</v>
+        <v>535512</v>
       </c>
       <c r="R24" t="n">
-        <v>6722342</v>
+        <v>6722482</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3227,22 +3248,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3257,26 +3278,26 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Ulf Magnusson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Ulf Magnusson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129865280</v>
+        <v>131939773</v>
       </c>
       <c r="B25" t="n">
-        <v>57823</v>
+        <v>57972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3302,20 +3323,20 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Jungfruberget östra, Dlr</t>
+          <t>Jungfruberget 2, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>535504</v>
+        <v>535462</v>
       </c>
       <c r="R25" t="n">
-        <v>6722415</v>
+        <v>6722514</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3342,22 +3363,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>födosöks hack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3384,57 +3410,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129863936</v>
+        <v>131939942</v>
       </c>
       <c r="B26" t="n">
-        <v>57953</v>
+        <v>57972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103035</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Jungfruberget östra, Dlr</t>
+          <t>Jungfruberget 2, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>535285</v>
+        <v>535387</v>
       </c>
       <c r="R26" t="n">
-        <v>6722314</v>
+        <v>6722492</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3461,22 +3483,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3496,21 +3518,25 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130163497</v>
+        <v>133820560</v>
       </c>
       <c r="B27" t="n">
-        <v>57851</v>
+        <v>57972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3532,16 +3558,24 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Jungfruberget, Dlr</t>
+          <t>Jungfruberget östra, Jungfruberget östra, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>535512</v>
+        <v>535142</v>
       </c>
       <c r="R27" t="n">
-        <v>6722482</v>
+        <v>6722295</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3568,22 +3602,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3598,22 +3632,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulf Magnusson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulf Magnusson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130164260</v>
+        <v>126050897</v>
       </c>
       <c r="B28" t="n">
-        <v>8451</v>
+        <v>57141</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3621,34 +3655,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>535322</v>
+        <v>535233</v>
       </c>
       <c r="R28" t="n">
-        <v>6722412</v>
+        <v>6722467</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3675,22 +3714,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På hranstubbe</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3705,22 +3749,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ulf Magnusson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ulf Magnusson</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131939733</v>
+        <v>129688110</v>
       </c>
       <c r="B29" t="n">
-        <v>93196</v>
+        <v>57141</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3728,37 +3772,48 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Jungfruberget 2, Dlr</t>
+          <t>Högtäkt, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>535434</v>
+        <v>535645</v>
       </c>
       <c r="R29" t="n">
-        <v>6722503</v>
+        <v>6722231</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3785,22 +3840,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3809,69 +3864,75 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Ulf Magnusson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Ulf Magnusson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131939966</v>
+        <v>129115043</v>
       </c>
       <c r="B30" t="n">
-        <v>8455</v>
+        <v>58388</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>103001</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Jungfruberget 2, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>535378</v>
+        <v>535199</v>
       </c>
       <c r="R30" t="n">
-        <v>6722481</v>
+        <v>6722263</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3898,22 +3959,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3922,7 +3983,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3937,35 +3997,31 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131939942</v>
+        <v>130053440</v>
       </c>
       <c r="B31" t="n">
-        <v>57972</v>
+        <v>58349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3974,27 +4030,19 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Jungfruberget 2, Dlr</t>
+          <t>Jungfruberget 2, Jungfruberget 2, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>535387</v>
+        <v>535384</v>
       </c>
       <c r="R31" t="n">
-        <v>6722492</v>
+        <v>6722509</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4023,7 +4071,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4033,7 +4081,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4056,18 +4104,14 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131939773</v>
+        <v>129116071</v>
       </c>
       <c r="B32" t="n">
-        <v>57972</v>
+        <v>58114</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4075,42 +4119,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Jungfruberget 2, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>535462</v>
+        <v>535283</v>
       </c>
       <c r="R32" t="n">
-        <v>6722514</v>
+        <v>6722313</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4137,27 +4177,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:47</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>födosöks hack</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4177,66 +4212,67 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131939888</v>
+        <v>76027584</v>
       </c>
       <c r="B33" t="n">
-        <v>93264</v>
+        <v>58057</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Jungfruberget 2, Dlr</t>
+          <t>Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>535399</v>
+        <v>535305</v>
       </c>
       <c r="R33" t="n">
-        <v>6722505</v>
+        <v>6722309</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4260,22 +4296,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2018-10-10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2018-10-10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4284,33 +4310,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Brita Danielsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130053440</v>
+        <v>129863936</v>
       </c>
       <c r="B34" t="n">
-        <v>58327</v>
+        <v>58082</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4318,37 +4339,49 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>103035</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Jungfruberget 2, Jungfruberget 2, Dlr</t>
+          <t>Jungfruberget östra, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>535384</v>
+        <v>535285</v>
       </c>
       <c r="R34" t="n">
-        <v>6722509</v>
+        <v>6722314</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4372,22 +4405,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4407,14 +4440,14 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131939790</v>
+        <v>69624294</v>
       </c>
       <c r="B35" t="n">
         <v>8455</v>
@@ -4443,21 +4476,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Jungfruberget 2, Dlr</t>
+          <t>Lugnet, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>535449</v>
+        <v>535550</v>
       </c>
       <c r="R35" t="n">
-        <v>6722509</v>
+        <v>6722452</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4484,22 +4512,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>13:54</t>
+          <t>2017-04-24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>13:54</t>
+          <t>2017-04-24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4508,29 +4526,28 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131939876</v>
+        <v>126051559</v>
       </c>
       <c r="B36" t="n">
-        <v>93264</v>
+        <v>8455</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4538,44 +4555,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Jungfruberget 2, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>535389</v>
+        <v>535369</v>
       </c>
       <c r="R36" t="n">
-        <v>6722514</v>
+        <v>6722495</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4599,22 +4609,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4623,7 +4633,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4638,18 +4647,14 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131939924</v>
+        <v>126369844</v>
       </c>
       <c r="B37" t="n">
-        <v>93264</v>
+        <v>8455</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4657,48 +4662,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Jungfruberget 2, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>535402</v>
+        <v>535401</v>
       </c>
       <c r="R37" t="n">
-        <v>6722499</v>
+        <v>6722359</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4722,22 +4716,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4746,7 +4740,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4761,15 +4754,11 @@
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131939837</v>
+        <v>126371162</v>
       </c>
       <c r="B38" t="n">
         <v>8455</v>
@@ -4798,21 +4787,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Jungfruberget 2, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>535425</v>
+        <v>535354</v>
       </c>
       <c r="R38" t="n">
-        <v>6722501</v>
+        <v>6722340</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4839,22 +4823,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4863,7 +4847,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4882,53 +4865,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133820560</v>
+        <v>126372830</v>
       </c>
       <c r="B39" t="n">
-        <v>57972</v>
+        <v>8455</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Jungfruberget östra, Jungfruberget östra, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>535142</v>
+        <v>535212</v>
       </c>
       <c r="R39" t="n">
-        <v>6722295</v>
+        <v>6722317</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4955,22 +4930,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4994,6 +4969,813 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129688736</v>
+      </c>
+      <c r="B40" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Högtäkt, Högtäkt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>535536</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6722396</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Ulf Magnusson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Ulf Magnusson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>130164241</v>
+      </c>
+      <c r="B41" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>535322</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6722412</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Ulf Magnusson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Ulf Magnusson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>131939790</v>
+      </c>
+      <c r="B42" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Jungfruberget 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>535449</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6722509</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>131939837</v>
+      </c>
+      <c r="B43" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Jungfruberget 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>535425</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6722501</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>131939966</v>
+      </c>
+      <c r="B44" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Jungfruberget 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>535378</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6722481</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126054738</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>535311</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6722256</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Blom eller knopp</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126053951</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>535458</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6722324</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28385-2025 artfynd.xlsx
+++ b/artfynd/A 28385-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129098263</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129100061</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130037365</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131939733</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1259,6 +1284,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131939876</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1382,6 +1412,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131939888</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1505,6 +1540,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131939924</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1629,6 +1669,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129090798</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1745,6 +1790,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129702227</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1861,6 +1911,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129703661</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1972,6 +2027,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131939678</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2079,6 +2139,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126051147</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2191,6 +2256,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126051392</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2303,6 +2373,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126053644</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2415,6 +2490,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126053829</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2522,6 +2602,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126054200</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2629,6 +2714,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126370532</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2736,6 +2826,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126370901</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2843,6 +2938,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129098432</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2950,6 +3050,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688888</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3065,6 +3170,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129704155</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3180,6 +3290,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129865280</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3287,6 +3402,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130163497</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3407,6 +3527,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131939773</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3526,6 +3651,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131939942</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3641,6 +3771,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133820560</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3758,6 +3893,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126050897</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3879,6 +4019,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688110</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3998,6 +4143,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115043</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4105,6 +4255,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130053440</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4216,6 +4371,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129116071</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4325,6 +4485,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76027584</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4444,6 +4609,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129863936</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4541,6 +4711,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69624294</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4648,6 +4823,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126051559</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4755,6 +4935,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126369844</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4862,6 +5047,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126371162</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4969,6 +5159,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126372830</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5076,6 +5271,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688736</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5183,6 +5383,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130164241</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5296,6 +5501,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131939790</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5409,6 +5619,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131939837</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5526,6 +5741,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131939966</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5652,6 +5872,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126054738</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5776,8 +6001,60 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126053951</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>